--- a/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
@@ -425,53 +425,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35_segun_loc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -486,47 +486,47 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
-        </is>
-      </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_miss</t>
+          <t>dif_mean_age_player_miss</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_val_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -541,20 +541,15 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -563,86 +558,657 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8235402696941593</v>
+        <v>1.893353762057464</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0593919809904479</v>
+        <v>-1.427276647604819</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3273385496542829</v>
+        <v>0.23652762990719</v>
       </c>
       <c r="E2" t="n">
-        <v>-5.822609107242445</v>
+        <v>0.2542526502150737</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.041372507400743</v>
+        <v>-0.3284580595838299</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.128603313993317</v>
+        <v>-1.671560200560242</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.675223175448459</v>
+        <v>-3.122646371379493</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.527168362536407</v>
+        <v>-1.674039137824915</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001707114181805365</v>
+        <v>0.5776893997235208</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.890328290954824</v>
+        <v>-1.535044131447915</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3753118973514278</v>
+        <v>-0.8119985868223683</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6607126801623241</v>
+        <v>-0.0211852453209775</v>
       </c>
       <c r="N2" t="n">
-        <v>2.086934260460904</v>
+        <v>-2.372167227058991</v>
       </c>
       <c r="O2" t="n">
-        <v>0.497269583898023</v>
+        <v>0.01329684745388514</v>
       </c>
       <c r="P2" t="n">
-        <v>1.212489595975037</v>
+        <v>0.4571830857474231</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.470640062220604</v>
+        <v>-1.029221231208445</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4699865561351577</v>
+        <v>-0.4331398063201062</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4803022935971346</v>
+        <v>-0.2819535161234449</v>
       </c>
       <c r="T2" t="n">
-        <v>0.559134738241447</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.695024035030358</v>
+        <v>-0.0661154369881759</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.424618000839671</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7868671261148011</v>
+        <v>-2.322185382033723</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9144193121739635</v>
+        <v>-3.057458054311152</v>
       </c>
       <c r="Y2" t="n">
-        <v>-1.361465060091115</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.320833909703814</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-0.07119147505746529</v>
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.9722655891195457</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.182079987343703</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.6361304325151106</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2243921636337838</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.840729625505378</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.31879933124156</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.50380288242282</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7466846238223573</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.03523975039230666</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-1.320028897518341</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4159185911974196</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1.095283929901465</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1.995194297492806</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.143320781427287</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.8868546245630283</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4358898637136545</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2849757210363311</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.996759295293527</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.3029568880369337</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.861282468290632</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.030830538928619</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05790036612601412</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6511704099863606</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.619536382657256</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-3.831700085220189</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-2.101587490548697</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7993489516256231</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-1.798320526286793</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1.61687500717631</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.5984490907420279</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1.865242532830553</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.1882632938834512</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0.9195901820365654</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.115850312905781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1.292671063639357</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.1177029379472708</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-1.743760994189897</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-2.148505749562837</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.9473682002599458</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.4058607250743463</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1040675519232354</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2243921636337838</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.4074641642858227</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.096250140049786</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.2189317507720959</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.951132893200945</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.68241824629753</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.81953741280323</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.7690056058726915</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.96018698452521</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.9089517523361204</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.6858367971295452</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.756493568833651</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0861612804779399</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.861282468290632</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.6030860532516675</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8655328941599443</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6511704099863606</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.407591957764225</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.704538943698102</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.8189424323773508</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.2104334514839536</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.1309033589739013</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.051925755049917</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.7908703725490448</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.3444684501452378</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01329684745388514</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1129897688014258</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.942017632959179</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.071039893988582</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.6049830370501406</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.477993341513951</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.292270715181312</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.8543661220305622</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.15602404693163</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9324483478038543</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.198273268049486</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2243921636337838</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.4226221978239861</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.4637026257939955</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.06048377861861561</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7466846238223573</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03523975039230666</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.07950229525957</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.767717775806588</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1882632938834512</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.5538847827814437</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.7325624006394567</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7717388311720572</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.793749259155448</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.4707725536635547</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.2560109230521751</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4345128738117022</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.608665921468182</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.213493253108276</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.915045615057096</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8563762850317925</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4226221978239861</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4637026257939955</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5776893997235208</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-1.535044131447915</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8824780876069821</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.175712936163078</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1.358317838602114</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.222657695477903</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0269414395649264</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.6641026705081515</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.2489545368945525</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.2208038948780636</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.58709277321538</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.2927459286941094</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.466762141181453</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.6761155995867568</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6380203517706502</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.273365817195405</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.43505353743312</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4226221978239861</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4637026257939955</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4.151047707521328</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2201318341446022</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3741350852781769</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-1.752976781584129</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3314311421593466</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.4164171301285576</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9734730611664182</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.7553823106832251</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.8254595347545106</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.8291983149498737</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.6401849707213183</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6220430864240817</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5925424263660467</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.0720576692122892</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,77 +558,77 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.893353762057464</v>
+        <v>1.861282468290632</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.427276647604819</v>
+        <v>-0.6761155995867568</v>
       </c>
       <c r="D2" t="n">
-        <v>0.23652762990719</v>
+        <v>-0.05790036612601412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2542526502150737</v>
+        <v>0.6511704099863606</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3284580595838299</v>
+        <v>4.731022129346915</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.671560200560242</v>
+        <v>-4.410158059951613</v>
       </c>
       <c r="H2" t="n">
-        <v>-3.122646371379493</v>
+        <v>0.4226221978239861</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.674039137824915</v>
+        <v>-0.8189424323773508</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5776893997235208</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.535044131447915</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8119985868223683</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0211852453209775</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.372167227058991</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01329684745388514</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4571830857474231</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.029221231208445</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.4331398063201062</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2819535161234449</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0661154369881759</v>
+        <v>0.4396759597722645</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-2.322185382033723</v>
+        <v>-1.181214972609025</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.057458054311152</v>
+        <v>-1.429810932833309</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -640,77 +640,77 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1.893353762057464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9722655891195457</v>
+        <v>0.2732685027694048</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.182079987343703</v>
+        <v>-1.463124892648125</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6361304325151106</v>
+        <v>1.273365817195405</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3284580595838299</v>
+        <v>4.731022129346915</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2243921636337838</v>
+        <v>1.699021780229138</v>
       </c>
       <c r="H3" t="n">
-        <v>1.840729625505378</v>
+        <v>1.131675911664682</v>
       </c>
       <c r="I3" t="n">
         <v>1.31879933124156</v>
       </c>
       <c r="J3" t="n">
-        <v>0.50380288242282</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7466846238223573</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03523975039230666</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.320028897518341</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4159185911974196</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.095283929901465</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.995194297492806</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.143320781427287</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8868546245630283</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4358898637136545</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2849757210363311</v>
+        <v>-0.1504069267300948</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.996759295293527</v>
+        <v>2.322065429987639</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3029568880369337</v>
+        <v>3.097884883489304</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -722,77 +722,77 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.861282468290632</v>
+        <v>1.925425055824297</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.030830538928619</v>
+        <v>1.118324681789725</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05790036612601412</v>
+        <v>0.9993638014477644</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6511704099863606</v>
+        <v>-0.8399530659111768</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3284580595838299</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.619536382657256</v>
+        <v>-0.09159989706522059</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.831700085220189</v>
+        <v>-0.9954852298574057</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.101587490548697</v>
+        <v>-0.3913940796535688</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7993489516256231</v>
+        <v>1.267296894530061</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.798320526286793</v>
+        <v>-1.184008938329411</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.61687500717631</v>
+        <v>1.221373422492852</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5984490907420279</v>
+        <v>1.133342445521124</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.865242532830553</v>
+        <v>1.007330734463931</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1882632938834512</v>
+        <v>2.835138826176593</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9195901820365654</v>
+        <v>2.350246328950407</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.115850312905781</v>
+        <v>1.709167974043758</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.292671063639357</v>
+        <v>0.1194160019565543</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.6718931298621182</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1177029379472708</v>
+        <v>1.000486166185128</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.743760994189897</v>
+        <v>-0.6458155556522062</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.148505749562837</v>
+        <v>-0.08282492958874885</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -804,59 +804,59 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.893353762057464</v>
+        <v>1.925425055824297</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.9473682002599458</v>
+        <v>1.932082483809292</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4058607250743463</v>
+        <v>-0.2184974548713982</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1040675519232354</v>
+        <v>0.8120830152990445</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3284580595838299</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2243921636337838</v>
+        <v>-0.7235840184632294</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.4226221978239861</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0.8189424323773508</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4074641642858227</v>
+        <v>-0.3877610930056364</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.096250140049786</v>
+        <v>0.711581104510507</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2189317507720959</v>
+        <v>-0.1003183835620414</v>
       </c>
       <c r="M5" t="n">
-        <v>1.951132893200945</v>
+        <v>-0.2136065271279943</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.68241824629753</v>
+        <v>0.3990211013898049</v>
       </c>
       <c r="O5" t="n">
-        <v>0.81953741280323</v>
+        <v>0.4970411866634921</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7690056058726915</v>
+        <v>0.5948604125258214</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96018698452521</v>
+        <v>-0.0981689014226961</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.9089517523361204</v>
+        <v>-0.009513686641332543</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -865,16 +865,16 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6858367971295452</v>
+        <v>0.02013929107117643</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.756493568833651</v>
+        <v>0.2835029409490984</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0861612804779399</v>
+        <v>-0.1224709058192108</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -886,77 +886,77 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.861282468290632</v>
+        <v>1.893353762057464</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.6030860532516675</v>
+        <v>-1.427276647604819</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8655328941599443</v>
+        <v>0.23652762990719</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6511704099863606</v>
+        <v>0.2542526502150737</v>
       </c>
       <c r="F6" t="n">
         <v>-0.3284580595838299</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.407591957764225</v>
+        <v>-1.671560200560242</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.704538943698102</v>
+        <v>-0.9954852298574057</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8189424323773508</v>
+        <v>-1.674039137824915</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2104334514839536</v>
+        <v>0.5776893997235208</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1309033589739013</v>
+        <v>-1.535044131447915</v>
       </c>
       <c r="L6" t="n">
-        <v>1.051925755049917</v>
+        <v>-0.8119985868223683</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7908703725490448</v>
+        <v>-0.0211852453209775</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3444684501452378</v>
+        <v>-2.372167227058991</v>
       </c>
       <c r="O6" t="n">
         <v>0.01329684745388514</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1129897688014258</v>
+        <v>0.4571830857474231</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.942017632959179</v>
+        <v>-1.029221231208445</v>
       </c>
       <c r="R6" t="n">
-        <v>1.071039893988582</v>
+        <v>-0.4331398063201062</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6049830370501406</v>
+        <v>-0.2819535161234449</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.477993341513951</v>
+        <v>0.100181265474527</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.292270715181312</v>
+        <v>-2.32066753000793</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8543661220305622</v>
+        <v>-3.126727212124239</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -968,20 +968,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1.893353762057464</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.15602404693163</v>
+        <v>0.9722655891195457</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9324483478038543</v>
+        <v>-1.182079987343703</v>
       </c>
       <c r="E7" t="n">
-        <v>1.198273268049486</v>
+        <v>-0.6361304325151106</v>
       </c>
       <c r="F7" t="n">
         <v>-0.3284580595838299</v>
@@ -990,13 +990,13 @@
         <v>0.2243921636337838</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4226221978239861</v>
+        <v>1.131675911664682</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4637026257939955</v>
+        <v>1.31879933124156</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06048377861861561</v>
+        <v>0.50380288242282</v>
       </c>
       <c r="K7" t="n">
         <v>0.7466846238223573</v>
@@ -1005,40 +1005,40 @@
         <v>0.03523975039230666</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.07950229525957</v>
+        <v>-1.320028897518341</v>
       </c>
       <c r="N7" t="n">
-        <v>1.767717775806588</v>
+        <v>0.4159185911974196</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1882632938834512</v>
+        <v>-1.095283929901465</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5538847827814437</v>
+        <v>-1.995194297492806</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.7325624006394567</v>
+        <v>-1.143320781427287</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7717388311720572</v>
+        <v>0.8868546245630283</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.793749259155448</v>
+        <v>0.4358898637136545</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4707725536635547</v>
+        <v>0.2738376992217997</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2560109230521751</v>
+        <v>0.9854223599850144</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4345128738117022</v>
+        <v>0.3530148273661316</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1050,77 +1050,77 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.893353762057464</v>
+        <v>1.861282468290632</v>
       </c>
       <c r="C8" t="n">
-        <v>1.608665921468182</v>
+        <v>-1.030830538928619</v>
       </c>
       <c r="D8" t="n">
-        <v>1.213493253108276</v>
+        <v>-0.05790036612601412</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.915045615057096</v>
+        <v>0.6511704099863606</v>
       </c>
       <c r="F8" t="n">
         <v>-0.3284580595838299</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8563762850317925</v>
+        <v>-2.619536382657256</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4226221978239861</v>
+        <v>-1.704538943698102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4637026257939955</v>
+        <v>-2.101587490548697</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5776893997235208</v>
+        <v>0.7993489516256231</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.535044131447915</v>
+        <v>-1.798320526286793</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8824780876069821</v>
+        <v>-1.61687500717631</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.175712936163078</v>
+        <v>-0.5984490907420279</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.358317838602114</v>
+        <v>-1.865242532830553</v>
       </c>
       <c r="O8" t="n">
-        <v>1.222657695477903</v>
+        <v>-0.1882632938834512</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0269414395649264</v>
+        <v>-0.9195901820365654</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.6641026705081515</v>
+        <v>1.115850312905781</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2489545368945525</v>
+        <v>-1.292671063639357</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2208038948780636</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.58709277321538</v>
+        <v>-0.1391295882216923</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2927459286941094</v>
+        <v>-1.642294083573278</v>
       </c>
       <c r="X8" t="n">
-        <v>1.466762141181453</v>
+        <v>-2.160838488834761</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1132,82 +1132,410 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1.893353762057464</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.6761155995867568</v>
+        <v>-0.9473682002599458</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6380203517706502</v>
+        <v>-0.4058607250743463</v>
       </c>
       <c r="E9" t="n">
-        <v>1.273365817195405</v>
+        <v>0.1040675519232354</v>
       </c>
       <c r="F9" t="n">
         <v>-0.3284580595838299</v>
       </c>
       <c r="G9" t="n">
+        <v>0.2243921636337838</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.4074641642858227</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.096250140049786</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.2189317507720959</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.951132893200945</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.68241824629753</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.81953741280323</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.7690056058726915</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.96018698452521</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.9089517523361204</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.8250296439591507</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.7620941299192476</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.07358847487851362</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.861282468290632</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.6030860532516675</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8655328941599443</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6511704099863606</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.407591957764225</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.9954852298574057</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.8189424323773508</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.2104334514839536</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.1309033589739013</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.051925755049917</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.7908703725490448</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.3444684501452378</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01329684745388514</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1129897688014258</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.942017632959179</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.071039893988582</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.6049830370501406</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1.557107559576246</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.294513279131513</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.826350330472759</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.15602404693163</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9324483478038543</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.198273268049486</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2243921636337838</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4226221978239861</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4637026257939955</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.06048377861861561</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7466846238223573</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.03523975039230666</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-1.07950229525957</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.767717775806588</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.1882632938834512</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5538847827814437</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.7325624006394567</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.7717388311720572</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.793749259155448</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.4436010464518569</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2467783391177854</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.404159322181043</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.608665921468182</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.213493253108276</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.915045615057096</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8563762850317925</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4226221978239861</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4637026257939955</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5776893997235208</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1.535044131447915</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.8824780876069821</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.175712936163078</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-1.358317838602114</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.222657695477903</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0269414395649264</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.6641026705081515</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.2489545368945525</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.2208038948780636</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.412496341290419</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.28366842991719</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.539020266338998</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.0720576692122892</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.893353762057464</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.6761155995867568</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.6380203517706502</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.273365817195405</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.3284580595838299</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.43505353743312</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.4226221978239861</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H13" t="n">
+        <v>-0.2864315160167099</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.4637026257939955</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J13" t="n">
         <v>-4.151047707521328</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K13" t="n">
         <v>0.2201318341446022</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L13" t="n">
         <v>0.3741350852781769</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M13" t="n">
         <v>-1.752976781584129</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N13" t="n">
         <v>0.3314311421593466</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O13" t="n">
         <v>0.4164171301285576</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P13" t="n">
         <v>0.9734730611664182</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q13" t="n">
         <v>-0.7553823106832251</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R13" t="n">
         <v>0.8254595347545106</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S13" t="n">
         <v>-0.8291983149498737</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.6401849707213183</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.6220430864240817</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.5925424263660467</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.8208469001217307</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.7308217262720602</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6480357181534682</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.0720576692122892</v>
       </c>
     </row>

--- a/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,110 +446,145 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>h2h_3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -562,28 +597,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.861282468290632</v>
+        <v>1.889489013008169</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.6761155995867568</v>
+        <v>-0.704468021979111</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05790036612601412</v>
+        <v>-0.07034397800590414</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6511704099863606</v>
+        <v>-1.506772409325606</v>
       </c>
       <c r="F2" t="n">
-        <v>4.731022129346915</v>
+        <v>0.6889245125344139</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.410158059951613</v>
+        <v>2.840859831371093</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4226221978239861</v>
+        <v>-0.8236903667825567</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8189424323773508</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -619,22 +654,43 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4396759597722645</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.181214972609025</v>
+        <v>-0.3357510717955756</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.429810932833309</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.4137566348804382</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.0720576692122892</v>
+        <v>0.5110169837643742</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.171075143427464</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.24362140838506</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.465570377153729</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="3">
@@ -644,28 +700,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.893353762057464</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2732685027694048</v>
+        <v>0.2629888994981002</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.463124892648125</v>
+        <v>-1.506213904360662</v>
       </c>
       <c r="E3" t="n">
-        <v>1.273365817195405</v>
+        <v>1.239657046717853</v>
       </c>
       <c r="F3" t="n">
-        <v>4.731022129346915</v>
+        <v>1.309843990073082</v>
       </c>
       <c r="G3" t="n">
-        <v>1.699021780229138</v>
+        <v>2.840859831371093</v>
       </c>
       <c r="H3" t="n">
-        <v>1.131675911664682</v>
+        <v>1.319909512694158</v>
       </c>
       <c r="I3" t="n">
-        <v>1.31879933124156</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -701,22 +757,43 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1504069267300948</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.322065429987639</v>
+        <v>1.662728384174271</v>
       </c>
       <c r="X3" t="n">
-        <v>3.097884883489304</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.1754102577604576</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0720576692122892</v>
+        <v>-0.09227751869954864</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.6759579463595338</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.306678777026949</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>3.158569408851771</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="4">
@@ -726,137 +803,158 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.925425055824297</v>
+        <v>1.955737588137495</v>
       </c>
       <c r="C4" t="n">
-        <v>1.118324681789725</v>
+        <v>1.124131873560233</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9993638014477644</v>
+        <v>1.009977204680057</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8399530659111768</v>
+        <v>-0.2462531149105227</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3284580595838299</v>
+        <v>-0.7991411319117055</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.09159989706522059</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9954852298574057</v>
+        <v>-0.3949703908872138</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3913940796535688</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.267296894530061</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.184008938329411</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.221373422492852</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.133342445521124</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.007330734463931</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.835138826176593</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.350246328950407</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.709167974043758</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1194160019565543</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6718931298621182</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.000486166185128</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6458155556522062</v>
+        <v>-1.115823850975572</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.08282492958874885</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.238276137129546</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0720576692122892</v>
+        <v>1.08346879381113</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9456763357441345</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.6551998799866557</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.06508397140443559</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.925425055824297</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.932082483809292</v>
+        <v>-1.469928443367674</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2184974548713982</v>
+        <v>0.2305049589446166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8120830152990445</v>
+        <v>-1.281381542112313</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3284580595838299</v>
+        <v>0.2928207078976771</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7235840184632294</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4226221978239861</v>
+        <v>-1.681130318573242</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8189424323773508</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3877610930056364</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.711581104510507</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1003183835620414</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2136065271279943</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3990211013898049</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4970411866634921</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5948604125258214</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0981689014226961</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.009513686641332543</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -865,244 +963,307 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02013929107117643</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2835029409490984</v>
+        <v>-1.718437300512148</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1224709058192108</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.2305173607731116</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.0720576692122892</v>
+        <v>0.04668943494044678</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.6569918047369289</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.277517191397914</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-3.165814218100496</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.893353762057464</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.427276647604819</v>
+        <v>0.9752923471791237</v>
       </c>
       <c r="D6" t="n">
-        <v>0.23652762990719</v>
+        <v>-1.21903991908971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2542526502150737</v>
+        <v>-0.4132093128462953</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3284580595838299</v>
+        <v>-0.5957364754766246</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.671560200560242</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9954852298574057</v>
+        <v>1.319909512694158</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.674039137824915</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5776893997235208</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.535044131447915</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8119985868223683</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0211852453209775</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.372167227058991</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01329684745388514</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4571830857474231</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.029221231208445</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.4331398063201062</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2819535161234449</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.100181265474527</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.32066753000793</v>
+        <v>0.5947566951524392</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.126727212124239</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.7622510480967561</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0720576692122892</v>
+        <v>0.260547650348467</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1.592769223369506</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1.615580035498994</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.3479538264274055</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.893353762057464</v>
+        <v>1.889489013008169</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9722655891195457</v>
+        <v>-1.065935443190377</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.182079987343703</v>
+        <v>-0.07034397800590414</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6361304325151106</v>
+        <v>1.874090598873789</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3284580595838299</v>
+        <v>0.6889245125344139</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2243921636337838</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H7" t="n">
-        <v>1.131675911664682</v>
+        <v>-2.109850294468585</v>
       </c>
       <c r="I7" t="n">
-        <v>1.31879933124156</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.50380288242282</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7466846238223573</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03523975039230666</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.320028897518341</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4159185911974196</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.095283929901465</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.995194297492806</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.143320781427287</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8868546245630283</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4358898637136545</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2738376992217997</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9854223599850144</v>
+        <v>-1.071182668386786</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3530148273661316</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.3839212035468028</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.0720576692122892</v>
+        <v>-0.1393798575332207</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1651372401436337</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.967830770130592</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-2.187866957432893</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>hnqZAAAk</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.861282468290632</v>
+        <v>1.889489013008169</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.030830538928619</v>
+        <v>-0.6300482587885563</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.05790036612601412</v>
+        <v>0.8732276878843653</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6511704099863606</v>
+        <v>0.4048760570389904</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3284580595838299</v>
+        <v>0.6889245125344139</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.619536382657256</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.704538943698102</v>
+        <v>-0.8236903667825567</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.101587490548697</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7993489516256231</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.798320526286793</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.61687500717631</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5984490907420279</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.865242532830553</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1882632938834512</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9195901820365654</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.115850312905781</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.292671063639357</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1111,80 +1272,101 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1391295882216923</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.642294083573278</v>
+        <v>-0.4330870707299789</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.160838488834761</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-2.181689102007081</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.0720576692122892</v>
+        <v>-1.589308112449137</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8434547956113199</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.4828219455714508</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.8298605448890463</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>nDzACNof</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.893353762057464</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.9473682002599458</v>
+        <v>-1.19351218008847</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4058607250743463</v>
+        <v>0.9416024462822109</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1040675519232354</v>
+        <v>1.874090598873789</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3284580595838299</v>
+        <v>1.234905432439105</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2243921636337838</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.462469560903472</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4074641642858227</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.096250140049786</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2189317507720959</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.951132893200945</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.68241824629753</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.81953741280323</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7690056058726915</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96018698452521</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.9089517523361204</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1193,350 +1375,249 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8250296439591507</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7620941299192476</v>
+        <v>0.6301990886017149</v>
       </c>
       <c r="X9" t="n">
-        <v>0.07358847487851362</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.4046402530840541</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.0720576692122892</v>
+        <v>-0.4664057980708722</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.7590711982873541</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.498552715482135</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.4223349043774781</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QyafIhIF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.861282468290632</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.6030860532516675</v>
+        <v>1.6238074264111</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8655328941599443</v>
+        <v>1.228776431553162</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6511704099863606</v>
+        <v>1.239657046717853</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3284580595838299</v>
+        <v>-0.8740796895456828</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.407591957764225</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9954852298574057</v>
+        <v>0.462469560903472</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8189424323773508</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2104334514839536</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1309033589739013</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.051925755049917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7908703725490448</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3444684501452378</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01329684745388514</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1129897688014258</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.942017632959179</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.071039893988582</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6049830370501406</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.557107559576246</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.294513279131513</v>
+        <v>-0.6400763908151096</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.826350330472759</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.3820979271875321</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0720576692122892</v>
+        <v>1.447207749403058</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.26485973527224</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.102992368163177</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.577195987149263</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>hO0nKEm3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.893353762057464</v>
+        <v>1.922613300572832</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.15602404693163</v>
+        <v>-0.704468021979111</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9324483478038543</v>
+        <v>0.6407535093316902</v>
       </c>
       <c r="E11" t="n">
-        <v>1.198273268049486</v>
+        <v>-1.506772409325606</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3284580595838299</v>
+        <v>1.309843990073082</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2243921636337838</v>
+        <v>-0.3520061035596279</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4226221978239861</v>
+        <v>0.462469560903472</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4637026257939955</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06048377861861561</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7466846238223573</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03523975039230666</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.07950229525957</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.767717775806588</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1882632938834512</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5538847827814437</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.7325624006394567</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7717388311720572</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.793749259155448</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4436010464518569</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2467783391177854</v>
+        <v>0.530470079335345</v>
       </c>
       <c r="X11" t="n">
-        <v>0.404159322181043</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0.3198161133065371</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.0720576692122892</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>QyafIhIF</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.893353762057464</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.608665921468182</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.213493253108276</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.915045615057096</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.3284580595838299</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.8563762850317925</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4226221978239861</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4637026257939955</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5776893997235208</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-1.535044131447915</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.8824780876069821</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-1.175712936163078</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-1.358317838602114</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.222657695477903</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.0269414395649264</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-0.6641026705081515</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-0.2489545368945525</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-0.2208038948780636</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.412496341290419</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.28366842991719</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.539020266338998</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>-0.0720576692122892</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>hO0nKEm3</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.893353762057464</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.6761155995867568</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.6380203517706502</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1.273365817195405</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.3284580595838299</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.43505353743312</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.2864315160167099</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4637026257939955</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-4.151047707521328</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2201318341446022</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.3741350852781769</v>
-      </c>
-      <c r="M13" t="n">
-        <v>-1.752976781584129</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.3314311421593466</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.4164171301285576</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.9734730611664182</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-0.7553823106832251</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.8254595347545106</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.8291983149498737</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-0.8208469001217307</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.7308217262720602</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.6480357181534682</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>-0.0720576692122892</v>
+        <v>-0.7779083362684897</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7566327142496628</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.1528478407699059</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6488950518885849</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.0732877462472411</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_selected_nan.xlsx
@@ -425,38 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_team_home</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home</t>
+          <t>id_team_away</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>h2h_35</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -466,127 +466,122 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35_segun_loc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3_segun_loc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_start</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -597,31 +592,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.889489013008169</v>
+        <v>-0.6768995524387025</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.704468021979111</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07034397800590414</v>
+        <v>-1.549162570724393</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.506772409325606</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6889245125344139</v>
+        <v>3.162616215670679</v>
       </c>
       <c r="G2" t="n">
-        <v>2.840859831371093</v>
+        <v>-4.407455352050336</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8236903667825567</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-2.727527315002224</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -660,37 +655,34 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3357510717955756</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4137566348804382</v>
+        <v>-0.8793825739938163</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.5110169837643742</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-1.728333427653596</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.171075143427464</v>
+        <v>-2.772792663759897</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.24362140838506</v>
+        <v>-1.179967850909398</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.465570377153729</v>
+        <v>0.3754595479068735</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.0732877462472411</v>
+        <v>0.5924742172463189</v>
       </c>
     </row>
     <row r="3">
@@ -700,31 +692,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.922613300572832</v>
+        <v>0.2721579594185562</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2629888994981002</v>
+        <v>-1.462803413424689</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.506213904360662</v>
+        <v>1.219030312860256</v>
       </c>
       <c r="E3" t="n">
-        <v>1.239657046717853</v>
+        <v>1.278984086531297</v>
       </c>
       <c r="F3" t="n">
-        <v>1.309843990073082</v>
+        <v>3.162616215670679</v>
       </c>
       <c r="G3" t="n">
-        <v>2.840859831371093</v>
+        <v>1.698559871033212</v>
       </c>
       <c r="H3" t="n">
-        <v>1.319909512694158</v>
+        <v>1.324711601540324</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1.647678964320315</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -763,37 +755,34 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.662728384174271</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.1754102577604576</v>
+        <v>1.910742552584788</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.09227751869954864</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.122412397300717</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.6759579463595338</v>
+        <v>5.823306420216245</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1.306678777026949</v>
+        <v>2.336542661990114</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.158569408851771</v>
+        <v>-0.268628646594458</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.0732877462472411</v>
+        <v>-0.7360289509449764</v>
       </c>
     </row>
     <row r="4">
@@ -803,31 +792,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.955737588137495</v>
+        <v>1.116923437005787</v>
       </c>
       <c r="C4" t="n">
-        <v>1.124131873560233</v>
+        <v>1.008351687704268</v>
       </c>
       <c r="D4" t="n">
-        <v>1.009977204680057</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2462531149105227</v>
+        <v>-0.8430651861914329</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7991411319117055</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3520061035596279</v>
+        <v>-0.09113424607748329</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3949703908872138</v>
+        <v>-0.3927305149719172</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.1892768712128023</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -866,71 +855,68 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.115823850975572</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.238276137129546</v>
+        <v>-0.4661695781472107</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.08346879381113</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0.4651151130289514</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9456763357441345</v>
+        <v>-1.079639703620966</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.6551998799866557</v>
+        <v>-0.5213863423788073</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.06508397140443559</v>
+        <v>0.7171475541134533</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.0732877462472411</v>
+        <v>0.3462593151923172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.922613300572832</v>
+        <v>1.930401304312008</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.469928443367674</v>
+        <v>-0.2137956720932055</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2305049589446166</v>
+        <v>-0.3712081521777338</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.281381542112313</v>
+        <v>0.8157956665968937</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2928207078976771</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3520061035596279</v>
+        <v>-0.7227909932930227</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.681130318573242</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.4243240786429714</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -969,71 +955,68 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.718437300512148</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2305173607731116</v>
+        <v>-0.3405176435346139</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04668943494044678</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.1905440461747585</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.6569918047369289</v>
+        <v>-0.04852790190720657</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.277517191397914</v>
+        <v>0.154028811858041</v>
       </c>
       <c r="AE5" t="n">
-        <v>-3.165814218100496</v>
+        <v>0.203019874194122</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-0.0732877462472411</v>
+        <v>-0.4384178969825435</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>M3h3GWnS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.922613300572832</v>
+        <v>-1.427802199182907</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9752923471791237</v>
+        <v>0.2428308139849714</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.21903991908971</v>
+        <v>-1.321985647147537</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4132093128462953</v>
+        <v>0.2556608331878484</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5957364754766246</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3520061035596279</v>
+        <v>-1.670276114116332</v>
       </c>
       <c r="H6" t="n">
-        <v>1.319909512694158</v>
+        <v>-1.680812102356098</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.269125221894711</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1072,71 +1055,68 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5947566951524392</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7622510480967561</v>
+        <v>-1.90244514006844</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.260547650348467</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-3.118377882890405</v>
       </c>
       <c r="AB6" t="n">
-        <v>-1.592769223369506</v>
+        <v>-5.81313243484263</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>-1.615580035498994</v>
+        <v>-2.324938614718639</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.3479538264274055</v>
+        <v>0.2659117096392433</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-0.0732877462472411</v>
+        <v>0.7606756626308502</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>Eax2EqHs</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.889489013008169</v>
+        <v>0.9709145890277466</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.065935443190377</v>
+        <v>-1.18076940731758</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07034397800590414</v>
+        <v>-0.446933793370019</v>
       </c>
       <c r="E7" t="n">
-        <v>1.874090598873789</v>
+        <v>-0.6384005355227432</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6889245125344139</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3520061035596279</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.109850294468585</v>
+        <v>1.324711601540324</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.7361776561281197</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.134002875826239</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1175,71 +1155,68 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.071182668386786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3839212035468028</v>
+        <v>0.2108863063377306</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1393798575332207</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.4833357263605067</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1651372401436337</v>
+        <v>1.141700141060192</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.967830770130592</v>
+        <v>1.067308411068589</v>
       </c>
       <c r="AE7" t="n">
-        <v>-2.187866957432893</v>
+        <v>0.08546743624035702</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-0.0732877462472411</v>
+        <v>-1.572492244283348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>KbKTWiX8</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.889489013008169</v>
+        <v>-1.031492468956799</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.6300482587885563</v>
+        <v>-0.05263338288914304</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8732276878843653</v>
+        <v>1.858491282928442</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4048760570389904</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6889245125344139</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3520061035596279</v>
+        <v>-2.617761234939641</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8236903667825567</v>
+        <v>-2.110172631484159</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-2.180626530086907</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-1.704712312906831</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1278,68 +1255,65 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4330870707299789</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-2.181689102007081</v>
+        <v>-1.783726959063851</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.589308112449137</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-2.221894966058168</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8434547956113199</v>
+        <v>-3.556801636502492</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.4828219455714508</v>
+        <v>-1.884083062261185</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.8298605448890463</v>
+        <v>-0.05101724504959215</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.0732877462472411</v>
+        <v>0.1256523541628751</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>ruUIA1G6</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.922613300572832</v>
+        <v>-0.9480588415407764</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.19351218008847</v>
+        <v>-0.4018183428312783</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9416024462822109</v>
+        <v>-0.2786545907204963</v>
       </c>
       <c r="E9" t="n">
-        <v>1.874090598873789</v>
+        <v>0.1048553011161823</v>
       </c>
       <c r="F9" t="n">
-        <v>1.234905432439105</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3520061035596279</v>
+        <v>0.2246941275302864</v>
       </c>
       <c r="H9" t="n">
-        <v>0.462469560903472</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.3715771328512414</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1381,71 +1355,68 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6301990886017149</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4046402530840541</v>
+        <v>1.005451210704542</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.4664057980708722</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.08675415580748531</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.7590711982873541</v>
+        <v>0.6254660620133495</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.498552715482135</v>
+        <v>0.9190666570749939</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.4223349043774781</v>
+        <v>-0.141962606387194</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-0.0732877462472411</v>
+        <v>-0.1984516976288954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>hnqZAAAk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.922613300572832</v>
+        <v>-0.6038951284496825</v>
       </c>
       <c r="C10" t="n">
-        <v>1.6238074264111</v>
+        <v>0.8740497800342159</v>
       </c>
       <c r="D10" t="n">
-        <v>1.228776431553162</v>
+        <v>0.3776342996126424</v>
       </c>
       <c r="E10" t="n">
-        <v>1.239657046717853</v>
+        <v>0.6542183108058229</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8740796895456828</v>
+        <v>-0.3161939140908171</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3520061035596279</v>
+        <v>-0.406962619685253</v>
       </c>
       <c r="H10" t="n">
-        <v>0.462469560903472</v>
+        <v>-0.8220910440999777</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.7222244369793933</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.9950335157235638</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1484,140 +1455,334 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6400763908151096</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3820979271875321</v>
+        <v>-0.5532584264083256</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.447207749403058</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0.8946401627174633</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.26485973527224</v>
+        <v>-0.6110433304391785</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.102992368163177</v>
+        <v>-1.039414740262161</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.577195987149263</v>
+        <v>-1.319775082193424</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-0.0732877462472411</v>
+        <v>0.3739574572626534</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-1.156642910080833</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9412007338692419</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.858491282928442</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.203581320495464</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2246941275302864</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7361776561281197</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.6701977130784036</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.3448163449288419</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.307831181908703</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.2077737763464778</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.2683044833351454</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.6319492544233218</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.60709599807492</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.223234739976351</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.219030312860256</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.9184679522272658</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8563508747458258</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.006976609574363205</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4243240786429714</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.2037041538834944</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.618935694999978</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.4963478562605419</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.3950959388945559</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.416785489970804</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.471668708881815</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>hO0nKEm3</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1.922613300572832</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.704468021979111</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6407535093316902</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-1.506772409325606</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.309843990073082</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.3520061035596279</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.462469560903472</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.530470079335345</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>-0.3198161133065371</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.7779083362684897</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.7566327142496628</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>-0.1528478407699059</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.6488950518885849</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.0732877462472411</v>
+      <c r="B13" t="n">
+        <v>-0.6768995524387025</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6457365369951275</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.549162570724393</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.278984086531297</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.3161939140908171</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4352463766021329</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4659905432842035</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3715771328512414</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.2853547185402961</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7946923478262913</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.4200523063345913</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8013586140150831</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.5477467382570875</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.8854826934661758</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2520987607142808</v>
       </c>
     </row>
   </sheetData>
